--- a/assets/template/month_1.xlsx
+++ b/assets/template/month_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98896AA5-CD1A-4B81-A208-D5B6F2083745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B86BE3-9471-426A-891B-9CD99E19D94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="2370" windowWidth="28080" windowHeight="13110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,23 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
-    <r>
-      <t xml:space="preserve">KẾ HOẠCH NGHIÊN CỨU ĐỘ ỔN ĐỊNH HÀNG THÁNG
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>MONTHLY PLAN FOR STABILITY STUDY</t>
-    </r>
-  </si>
-  <si>
     <t>Khu vực
 Area</t>
   </si>
@@ -114,21 +97,19 @@
   <si>
     <t>Người phê duyệt / Ngày
 Approved by / Date</t>
+  </si>
+  <si>
+    <t>KẾ HOẠCH NGHIÊN CỨU ĐỘ ỔN ĐỊNH HÀNG THÁNG
+MONTHLY PLAN FOR STABILITY STUDY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -154,14 +135,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -227,75 +200,75 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,226 +616,220 @@
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.77734375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="5.77734375" style="24" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" style="24" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="24" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="24" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="24" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" style="24" customWidth="1"/>
+    <col min="8" max="9" width="7.88671875" style="24" customWidth="1"/>
+    <col min="10" max="10" width="9.77734375" style="24" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" style="24" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="24" customWidth="1"/>
+    <col min="13" max="13" width="7.21875" style="24" customWidth="1"/>
+    <col min="14" max="16384" width="8.77734375" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="18" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+    </row>
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-    </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+    </row>
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" s="1" customFormat="1" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-    </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="I4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16" t="s">
+      <c r="M4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="16" t="s">
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="5"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" spans="1:13" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-    </row>
-    <row r="6" spans="1:13" s="2" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" spans="1:13" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-    </row>
-    <row r="10" spans="1:13" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-    </row>
-    <row r="11" spans="1:13" s="2" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-    </row>
-    <row r="12" spans="1:13" s="2" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+    </row>
+    <row r="11" spans="1:13" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+    </row>
+    <row r="12" spans="1:13" s="1" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A11:F12"/>
-    <mergeCell ref="G11:M12"/>
-    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="D2:J2"/>
     <mergeCell ref="L2:M2"/>
@@ -878,13 +845,19 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="A11:F12"/>
+    <mergeCell ref="G11:M12"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.19685039370078741" top="0.51181102362204722" bottom="0.51181102362204722" header="0.23622047244094491" footer="0.23622047244094491"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;C&amp;12
 </oddHeader>
-    <oddFooter>&amp;L&amp;12Mã số phụ lục / &amp;"Times New Roman,Italic"Appendix No.&amp;"Times New Roman,Regular" 0002020_A03_03&amp;C&amp;12Ngày hiệu lực / &amp;"Times New Roman,Italic"Appendix effective &amp;"Times New Roman,Regular"28/05/2025&amp;R&amp;12Trang / Page &amp;P/&amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;12Mã số phụ lục / Appendix No. 0002020_A03_03&amp;C&amp;12Ngày hiệu lực / Appendix effective 28/05/2025&amp;R&amp;12Trang / Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
